--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SOLGALEO BOSCO SALESIANOS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SOLGALEO BOSCO SALESIANOS.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>38.2103</v>
+        <v>13.5198</v>
       </c>
       <c r="E2" t="n">
-        <v>41.3434</v>
+        <v>23.0349</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.1333</v>
+        <v>-9.515000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>-10.7453</v>
@@ -610,13 +610,13 @@
         <v>45.2405</v>
       </c>
       <c r="S2" t="n">
-        <v>40.5313</v>
+        <v>15.8408</v>
       </c>
       <c r="T2" t="n">
-        <v>28.1556</v>
+        <v>9.8469</v>
       </c>
       <c r="U2" t="n">
-        <v>12.376</v>
+        <v>5.9939</v>
       </c>
       <c r="V2" t="n">
         <v>19.9793</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GAYE</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.200999999999999</v>
+        <v>1.2816</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6395</v>
+        <v>4.0567</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5616</v>
+        <v>-2.775</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5312</v>
+        <v>2.1288</v>
       </c>
       <c r="H3" t="n">
-        <v>9.1432</v>
+        <v>2.8206</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.6117</v>
+        <v>-0.6918</v>
       </c>
       <c r="J3" t="n">
-        <v>16.4647</v>
+        <v>7.2577</v>
       </c>
       <c r="K3" t="n">
-        <v>14.5604</v>
+        <v>7.1671</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9042</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.9335</v>
+        <v>-5.1289</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.4174</v>
+        <v>-4.3466</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.516</v>
+        <v>-0.7824</v>
       </c>
       <c r="P3" t="n">
-        <v>-13.3177</v>
+        <v>-0.7834000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-24.6768</v>
+        <v>-3.1335</v>
       </c>
       <c r="R3" t="n">
-        <v>11.3592</v>
+        <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>11.6408</v>
+        <v>-0.2239</v>
       </c>
       <c r="T3" t="n">
-        <v>7.1569</v>
+        <v>-0.17</v>
       </c>
       <c r="U3" t="n">
-        <v>4.4841</v>
+        <v>-0.054</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6532999999999999</v>
+        <v>0.1602</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6948</v>
+        <v>0.1026</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.3481</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>S. SANCHEZ CRUZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7019</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>4.159000000000001</v>
+        <v>1.1341</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.4571</v>
+        <v>-0.1679</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1288</v>
+        <v>0.981</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8206</v>
+        <v>-0.4083</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6918</v>
+        <v>1.3893</v>
       </c>
       <c r="J4" t="n">
-        <v>7.2577</v>
+        <v>1.2529</v>
       </c>
       <c r="K4" t="n">
-        <v>7.1671</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09039999999999999</v>
+        <v>1.2529</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.1289</v>
+        <v>-0.2719</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.3466</v>
+        <v>-0.4083</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7824</v>
+        <v>0.1364</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7834000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1335</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3502</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1964</v>
+        <v>-0.0149</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.1188</v>
       </c>
       <c r="U4" t="n">
-        <v>0.264</v>
+        <v>0.104</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1602</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1026</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SANCHEZ CRUZ</t>
+          <t>O. DJAMGOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9394</v>
+        <v>0.8011999999999997</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1341</v>
+        <v>8.053900000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1946</v>
+        <v>-7.2528</v>
       </c>
       <c r="G5" t="n">
-        <v>0.981</v>
+        <v>9.545199999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4083</v>
+        <v>-4.276200000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3893</v>
+        <v>13.8212</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2529</v>
+        <v>20.3335</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4.4107</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2529</v>
+        <v>15.9229</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2719</v>
+        <v>-10.7885</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4083</v>
+        <v>-8.6868</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1364</v>
+        <v>-2.1017</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-5.2879</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-16.6471</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>11.3591</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0416</v>
+        <v>-1.2713</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1188</v>
+        <v>0.167</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0772</v>
+        <v>-1.4382</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.1848</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4.2006</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-6.3854</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02420000000000003</v>
+        <v>-0.03390000000000004</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0985</v>
+        <v>-1.9961</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1226</v>
+        <v>1.9623</v>
       </c>
       <c r="G6" t="n">
         <v>1.1051</v>
@@ -922,13 +922,13 @@
         <v>0.3916</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1725</v>
+        <v>0.1144</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1476</v>
+        <v>0.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02479999999999993</v>
+        <v>-0.1355</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6659</v>
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1031</v>
+        <v>-0.7473</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4911</v>
+        <v>-1.0817</v>
       </c>
       <c r="F7" t="n">
-        <v>0.388</v>
+        <v>0.3345</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5022</v>
@@ -1000,13 +1000,13 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8543000000000001</v>
+        <v>-0.4984</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6534</v>
+        <v>-0.2441</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2009</v>
+        <v>-0.2544</v>
       </c>
       <c r="V7" t="n">
         <v>0.0576</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GOMEZ CALLEJA</t>
+          <t>H. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1344</v>
+        <v>-2.1596</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8632</v>
+        <v>-1.533</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2713</v>
+        <v>-0.6267</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0154</v>
+        <v>-1.0499</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0602</v>
+        <v>-0.2364</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0756</v>
+        <v>-0.8135</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8883</v>
+        <v>-0.5802</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9595</v>
+        <v>0.102</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0712</v>
+        <v>-0.6822</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8729</v>
+        <v>-0.4698</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0197</v>
+        <v>-0.3386</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1468</v>
+        <v>-0.1313</v>
       </c>
       <c r="P8" t="n">
         <v>-0.9792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3445</v>
+        <v>-0.1305</v>
       </c>
       <c r="T8" t="n">
-        <v>0.207</v>
+        <v>0.0264</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5516</v>
+        <v>-0.1569</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8260999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ GONZALEZ</t>
+          <t>G. GOMEZ CALLEJA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3375</v>
+        <v>-2.2322</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7376</v>
+        <v>-1.0678</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5999</v>
+        <v>-1.1643</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0499</v>
+        <v>0.0154</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2364</v>
+        <v>-0.0602</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8135</v>
+        <v>0.0756</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5802</v>
+        <v>0.8883</v>
       </c>
       <c r="K9" t="n">
-        <v>0.102</v>
+        <v>0.9595</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6822</v>
+        <v>-0.0712</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4698</v>
+        <v>-0.8729</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3386</v>
+        <v>-1.0197</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1313</v>
+        <v>0.1468</v>
       </c>
       <c r="P9" t="n">
         <v>-0.9792</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3083</v>
+        <v>-0.4423</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1782</v>
+        <v>0.0023</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1301</v>
+        <v>-0.4446</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. DJAMGOZ</t>
+          <t>A. GAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1805</v>
+        <v>-2.6789</v>
       </c>
       <c r="E10" t="n">
-        <v>4.099299999999999</v>
+        <v>-1.9261</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.2798</v>
+        <v>-0.7528000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>9.545199999999999</v>
+        <v>6.5312</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.276200000000001</v>
+        <v>9.1432</v>
       </c>
       <c r="I10" t="n">
-        <v>13.8212</v>
+        <v>-2.6117</v>
       </c>
       <c r="J10" t="n">
-        <v>20.3335</v>
+        <v>16.4647</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4107</v>
+        <v>14.5604</v>
       </c>
       <c r="L10" t="n">
-        <v>15.9229</v>
+        <v>1.9042</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.7885</v>
+        <v>-9.9335</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.6868</v>
+        <v>-5.4174</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1017</v>
+        <v>-4.516</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.2879</v>
+        <v>-13.3177</v>
       </c>
       <c r="Q10" t="n">
-        <v>-16.6471</v>
+        <v>-24.6768</v>
       </c>
       <c r="R10" t="n">
-        <v>11.3591</v>
+        <v>11.3592</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.2527</v>
+        <v>4.7608</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.7876</v>
+        <v>2.5912</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.4652</v>
+        <v>2.1695</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1848</v>
+        <v>-0.6532999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>4.2006</v>
+        <v>3.6948</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.3854</v>
+        <v>-4.3481</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3106</v>
+        <v>-4.194500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.659800000000001</v>
+        <v>-4.8645</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3492</v>
+        <v>0.67</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1872</v>
@@ -1312,13 +1312,13 @@
         <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2845</v>
+        <v>0.4006</v>
       </c>
       <c r="T11" t="n">
-        <v>0.207</v>
+        <v>0.002299999999999976</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0774</v>
+        <v>0.3983</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6659</v>
@@ -1345,13 +1345,13 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.242599999999999</v>
+        <v>-4.496</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6652</v>
+        <v>-2.4237</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5775</v>
+        <v>-2.072</v>
       </c>
       <c r="G12" t="n">
         <v>-8.410299999999999</v>
@@ -1390,13 +1390,13 @@
         <v>12.3384</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.6569</v>
+        <v>0.08979999999999984</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8051999999999999</v>
+        <v>1.4361</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8515</v>
+        <v>-1.3463</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4841999999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.0715</v>
+        <v>-6.479799999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2678</v>
+        <v>8.714499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.3393</v>
+        <v>-15.1943</v>
       </c>
       <c r="G13" t="n">
-        <v>-16.816</v>
+        <v>-0.9815999999999987</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.363699999999999</v>
+        <v>0.202000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.4522</v>
+        <v>-1.183999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>6.221</v>
+        <v>45.06</v>
       </c>
       <c r="K13" t="n">
-        <v>6.299</v>
+        <v>28.6305</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.07789999999999997</v>
+        <v>16.4296</v>
       </c>
       <c r="M13" t="n">
-        <v>-23.0373</v>
+        <v>-46.0417</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.6626</v>
+        <v>-28.4281</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.3744</v>
+        <v>-17.6138</v>
       </c>
       <c r="P13" t="n">
-        <v>4.896199999999999</v>
+        <v>-19.7806</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.4927</v>
+        <v>-71.68049999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>19.3888</v>
+        <v>51.8996</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5721</v>
+        <v>-1.0734</v>
       </c>
       <c r="T13" t="n">
-        <v>8.334399999999999</v>
+        <v>1.1228</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.7619</v>
+        <v>-2.1959</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.723599999999999</v>
+        <v>15.3555</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2053999999999998</v>
+        <v>34.2129</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.929</v>
+        <v>-18.8571</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ALIK</t>
+          <t>A. HARRIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.5887</v>
+        <v>-13.6243</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.5801</v>
+        <v>-6.6022</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.0085</v>
+        <v>-7.022199999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.3447</v>
+        <v>-6.103200000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.2203</v>
+        <v>-21.733</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1242000000000001</v>
+        <v>15.6296</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9727000000000001</v>
+        <v>32.1007</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.8311</v>
+        <v>4.1404</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8583</v>
+        <v>27.9602</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.3719</v>
+        <v>-38.204</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.3894</v>
+        <v>-25.8733</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9825</v>
+        <v>-12.3306</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.7003</v>
+        <v>-30.1608</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.9467</v>
+        <v>-70.7013</v>
       </c>
       <c r="R14" t="n">
-        <v>7.2463</v>
+        <v>40.5404</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4029</v>
+        <v>-4.8237</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6457999999999999</v>
+        <v>-0.5943999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2429</v>
+        <v>-4.2297</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.1406</v>
+        <v>27.4637</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9852</v>
+        <v>32.5929</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.1258</v>
+        <v>-5.1294</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.7294</v>
+        <v>-16.085</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.651899999999999</v>
+        <v>-8.3284</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.077299999999999</v>
+        <v>-7.7567</v>
       </c>
       <c r="G15" t="n">
         <v>-3.364</v>
@@ -1624,13 +1624,13 @@
         <v>1.3707</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.4656</v>
+        <v>-2.8212</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4256</v>
+        <v>-1.1022</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.04</v>
+        <v>-1.719</v>
       </c>
       <c r="V15" t="n">
         <v>-5.1993</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>J. ALIK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.2467</v>
+        <v>-16.1731</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2049000000000012</v>
+        <v>-11.138</v>
       </c>
       <c r="F16" t="n">
-        <v>-20.042</v>
+        <v>-5.0351</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9815999999999987</v>
+        <v>-5.3447</v>
       </c>
       <c r="H16" t="n">
-        <v>0.202000000000001</v>
+        <v>-5.2203</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.183999999999999</v>
+        <v>-0.1242000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>45.06</v>
+        <v>-0.9727000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>28.6305</v>
+        <v>-1.8311</v>
       </c>
       <c r="L16" t="n">
-        <v>16.4296</v>
+        <v>0.8583</v>
       </c>
       <c r="M16" t="n">
-        <v>-46.0417</v>
+        <v>-4.3719</v>
       </c>
       <c r="N16" t="n">
-        <v>-28.4281</v>
+        <v>-3.3894</v>
       </c>
       <c r="O16" t="n">
-        <v>-17.6138</v>
+        <v>-0.9825</v>
       </c>
       <c r="P16" t="n">
-        <v>-19.7806</v>
+        <v>-4.7003</v>
       </c>
       <c r="Q16" t="n">
-        <v>-71.68049999999999</v>
+        <v>-11.9467</v>
       </c>
       <c r="R16" t="n">
-        <v>51.8996</v>
+        <v>7.2463</v>
       </c>
       <c r="S16" t="n">
-        <v>-14.8402</v>
+        <v>0.01249999999999996</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.7967</v>
+        <v>-0.2034</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.0438</v>
+        <v>0.2160000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>15.3555</v>
+        <v>-6.1406</v>
       </c>
       <c r="W16" t="n">
-        <v>34.2129</v>
+        <v>1.9852</v>
       </c>
       <c r="X16" t="n">
-        <v>-18.8571</v>
+        <v>-8.1258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. HARRIS</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>-28.7285</v>
+        <v>-21.7454</v>
       </c>
       <c r="E17" t="n">
-        <v>-17.2117</v>
+        <v>-4.647900000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.517</v>
+        <v>-17.0975</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.103200000000001</v>
+        <v>-16.816</v>
       </c>
       <c r="H17" t="n">
-        <v>-21.733</v>
+        <v>-6.363699999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>15.6296</v>
+        <v>-10.4522</v>
       </c>
       <c r="J17" t="n">
-        <v>32.1007</v>
+        <v>6.221</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1404</v>
+        <v>6.299</v>
       </c>
       <c r="L17" t="n">
-        <v>27.9602</v>
+        <v>-0.07789999999999997</v>
       </c>
       <c r="M17" t="n">
-        <v>-38.204</v>
+        <v>-23.0373</v>
       </c>
       <c r="N17" t="n">
-        <v>-25.8733</v>
+        <v>-12.6626</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.3306</v>
+        <v>-10.3744</v>
       </c>
       <c r="P17" t="n">
-        <v>-30.1608</v>
+        <v>4.896199999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-70.7013</v>
+        <v>-14.4927</v>
       </c>
       <c r="R17" t="n">
-        <v>40.5404</v>
+        <v>19.3888</v>
       </c>
       <c r="S17" t="n">
-        <v>-19.9281</v>
+        <v>-0.1020000000000003</v>
       </c>
       <c r="T17" t="n">
-        <v>-11.2035</v>
+        <v>3.4187</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.724499999999999</v>
+        <v>-3.5207</v>
       </c>
       <c r="V17" t="n">
-        <v>27.4637</v>
+        <v>-9.723599999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>32.5929</v>
+        <v>0.2053999999999998</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.1294</v>
+        <v>-9.929</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. VARELA BARRAL</t>
+          <t>M. TRAORE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-32.4878</v>
+        <v>-26.2901</v>
       </c>
       <c r="E18" t="n">
-        <v>-17.9019</v>
+        <v>-16.491</v>
       </c>
       <c r="F18" t="n">
-        <v>-14.5861</v>
+        <v>-9.798999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.405000000000001</v>
+        <v>-10.3358</v>
       </c>
       <c r="H18" t="n">
-        <v>8.0609</v>
+        <v>-6.202400000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-13.4661</v>
+        <v>-4.1333</v>
       </c>
       <c r="J18" t="n">
-        <v>16.3744</v>
+        <v>12.451</v>
       </c>
       <c r="K18" t="n">
-        <v>19.8152</v>
+        <v>8.559100000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.4411</v>
+        <v>3.8918</v>
       </c>
       <c r="M18" t="n">
-        <v>-21.7795</v>
+        <v>-22.7865</v>
       </c>
       <c r="N18" t="n">
-        <v>-11.7544</v>
+        <v>-14.7615</v>
       </c>
       <c r="O18" t="n">
-        <v>-10.0252</v>
+        <v>-8.0253</v>
       </c>
       <c r="P18" t="n">
-        <v>-16.4513</v>
+        <v>-22.3267</v>
       </c>
       <c r="Q18" t="n">
-        <v>-48.3743</v>
+        <v>-48.5703</v>
       </c>
       <c r="R18" t="n">
-        <v>31.9226</v>
+        <v>26.2434</v>
       </c>
       <c r="S18" t="n">
-        <v>4.0319</v>
+        <v>-2.1246</v>
       </c>
       <c r="T18" t="n">
-        <v>6.0431</v>
+        <v>-0.4777000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.0108</v>
+        <v>-1.6469</v>
       </c>
       <c r="V18" t="n">
-        <v>-14.6633</v>
+        <v>8.497300000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>8.0557</v>
+        <v>20.1068</v>
       </c>
       <c r="X18" t="n">
-        <v>-22.7189</v>
+        <v>-11.6092</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TRAORE</t>
+          <t>R. VARELA BARRAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-36.3748</v>
+        <v>-32.1969</v>
       </c>
       <c r="E19" t="n">
-        <v>-24.0997</v>
+        <v>-17.8925</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.275</v>
+        <v>-14.3049</v>
       </c>
       <c r="G19" t="n">
-        <v>-10.3358</v>
+        <v>-5.405000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.202400000000001</v>
+        <v>8.0609</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.1333</v>
+        <v>-13.4661</v>
       </c>
       <c r="J19" t="n">
-        <v>12.451</v>
+        <v>16.3744</v>
       </c>
       <c r="K19" t="n">
-        <v>8.559100000000001</v>
+        <v>19.8152</v>
       </c>
       <c r="L19" t="n">
-        <v>3.8918</v>
+        <v>-3.4411</v>
       </c>
       <c r="M19" t="n">
-        <v>-22.7865</v>
+        <v>-21.7795</v>
       </c>
       <c r="N19" t="n">
-        <v>-14.7615</v>
+        <v>-11.7544</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.0253</v>
+        <v>-10.0252</v>
       </c>
       <c r="P19" t="n">
-        <v>-22.3267</v>
+        <v>-16.4513</v>
       </c>
       <c r="Q19" t="n">
-        <v>-48.5703</v>
+        <v>-48.3743</v>
       </c>
       <c r="R19" t="n">
-        <v>26.2434</v>
+        <v>31.9226</v>
       </c>
       <c r="S19" t="n">
-        <v>-12.2092</v>
+        <v>4.322700000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-8.086399999999999</v>
+        <v>6.052499999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.1229</v>
+        <v>-1.7297</v>
       </c>
       <c r="V19" t="n">
-        <v>8.497300000000001</v>
+        <v>-14.6633</v>
       </c>
       <c r="W19" t="n">
-        <v>20.1068</v>
+        <v>8.0557</v>
       </c>
       <c r="X19" t="n">
-        <v>-11.6092</v>
+        <v>-22.7189</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-42.1541</v>
+        <v>-38.8935</v>
       </c>
       <c r="E20" t="n">
-        <v>-27.9436</v>
+        <v>-24.9531</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.2105</v>
+        <v>-13.9406</v>
       </c>
       <c r="G20" t="n">
         <v>-21.8281</v>
@@ -2014,13 +2014,13 @@
         <v>10.9672</v>
       </c>
       <c r="S20" t="n">
-        <v>-7.369</v>
+        <v>-4.1083</v>
       </c>
       <c r="T20" t="n">
-        <v>-5.345</v>
+        <v>-2.3545</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.0241</v>
+        <v>-1.7537</v>
       </c>
       <c r="V20" t="n">
         <v>-11.1945</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-68.4538</v>
+        <v>-60.8972</v>
       </c>
       <c r="E21" t="n">
-        <v>-38.0383</v>
+        <v>-35.0779</v>
       </c>
       <c r="F21" t="n">
-        <v>-30.4153</v>
+        <v>-25.8195</v>
       </c>
       <c r="G21" t="n">
         <v>-44.8435</v>
@@ -2092,13 +2092,13 @@
         <v>37.211</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.9068</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0562</v>
+        <v>4.0169</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.9632</v>
+        <v>-1.367</v>
       </c>
       <c r="V21" t="n">
         <v>-23.0124</v>
@@ -2125,19 +2125,19 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-255.0672</v>
+        <v>-232.3589</v>
       </c>
       <c r="E22" t="n">
-        <v>-107.5044</v>
+        <v>-95.02979999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-147.5631</v>
+        <v>-137.3295</v>
       </c>
       <c r="G22" t="n">
         <v>-116.6101</v>
       </c>
       <c r="H22" t="n">
-        <v>-53.51199999999999</v>
+        <v>-53.512</v>
       </c>
       <c r="I22" t="n">
         <v>-63.0994</v>
@@ -2149,7 +2149,7 @@
         <v>129.0072</v>
       </c>
       <c r="L22" t="n">
-        <v>39.80279999999999</v>
+        <v>39.8028</v>
       </c>
       <c r="M22" t="n">
         <v>-285.4221</v>
@@ -2170,13 +2170,13 @@
         <v>311.3957</v>
       </c>
       <c r="S22" t="n">
-        <v>-12.1506</v>
+        <v>10.5571</v>
       </c>
       <c r="T22" t="n">
-        <v>11.194</v>
+        <v>23.668</v>
       </c>
       <c r="U22" t="n">
-        <v>-23.3441</v>
+        <v>-13.1108</v>
       </c>
       <c r="V22" t="n">
         <v>-3.900299999999994</v>
